--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486988_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486988_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B. TRAORE</t>
+          <t>E. MARTINEZ PRETEL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.2264</v>
+        <v>5.8222</v>
       </c>
       <c r="E2" t="n">
-        <v>4.889</v>
+        <v>4.3589</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3374</v>
+        <v>1.4634</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.3194</v>
+        <v>-1.5062</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.8589</v>
+        <v>-0.7981</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4606</v>
+        <v>-0.7081</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5974</v>
+        <v>0.2972</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0847</v>
+        <v>0.6137</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5127</v>
+        <v>-0.3165</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.9168</v>
+        <v>-1.8034</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.9436</v>
+        <v>-1.4118</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.9732</v>
+        <v>-0.3916</v>
       </c>
       <c r="P2" t="n">
-        <v>1.4374</v>
+        <v>5.1336</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.0534</v>
+        <v>-0.2053</v>
       </c>
       <c r="R2" t="n">
-        <v>3.4908</v>
+        <v>5.3389</v>
       </c>
       <c r="S2" t="n">
-        <v>1.442</v>
+        <v>0.8939</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2589</v>
+        <v>1.6695</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1831</v>
+        <v>-0.7756</v>
       </c>
       <c r="V2" t="n">
-        <v>5.6664</v>
+        <v>1.301</v>
       </c>
       <c r="W2" t="n">
-        <v>5.0861</v>
+        <v>2.5975</v>
       </c>
       <c r="X2" t="n">
-        <v>0.5803</v>
+        <v>-1.2965</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. MARTINEZ PRETEL</t>
+          <t>B. TRAORE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.7623</v>
+        <v>5.8072</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6843</v>
+        <v>4.7069</v>
       </c>
       <c r="F3" t="n">
-        <v>1.078</v>
+        <v>1.1002</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.5062</v>
+        <v>-2.3194</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.7981</v>
+        <v>-1.8589</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.7081</v>
+        <v>-0.4606</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2972</v>
+        <v>0.5974</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6137</v>
+        <v>0.0847</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.3165</v>
+        <v>0.5127</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.8034</v>
+        <v>-2.9168</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.4118</v>
+        <v>-1.9436</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3916</v>
+        <v>-0.9732</v>
       </c>
       <c r="P3" t="n">
-        <v>5.1336</v>
+        <v>1.4374</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2053</v>
+        <v>-2.0534</v>
       </c>
       <c r="R3" t="n">
-        <v>5.3389</v>
+        <v>3.4908</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8339</v>
+        <v>1.0227</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9949</v>
+        <v>1.0768</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.161</v>
+        <v>-0.0541</v>
       </c>
       <c r="V3" t="n">
-        <v>1.301</v>
+        <v>5.6664</v>
       </c>
       <c r="W3" t="n">
-        <v>2.5975</v>
+        <v>5.0861</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2965</v>
+        <v>0.5803</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.1531</v>
+        <v>3.4441</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2426</v>
+        <v>1.9486</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9105</v>
+        <v>1.4955</v>
       </c>
       <c r="G4" t="n">
         <v>1.4664</v>
@@ -766,13 +766,13 @@
         <v>2.0534</v>
       </c>
       <c r="S4" t="n">
-        <v>3.927</v>
+        <v>2.218</v>
       </c>
       <c r="T4" t="n">
-        <v>3.2774</v>
+        <v>1.9834</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6496</v>
+        <v>0.2346</v>
       </c>
       <c r="V4" t="n">
         <v>-0.2402</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9644</v>
+        <v>2.5756</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8529</v>
+        <v>1.6122</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1115</v>
+        <v>0.9633</v>
       </c>
       <c r="G5" t="n">
         <v>1.1307</v>
@@ -844,13 +844,13 @@
         <v>3.2855</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6644</v>
+        <v>-0.0533</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1358</v>
+        <v>0.6236</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5286</v>
+        <v>-0.6768</v>
       </c>
       <c r="V5" t="n">
         <v>0.4715</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. OKENCHI</t>
+          <t>C. KNOWLES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.039</v>
+        <v>0.3165</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1018</v>
+        <v>-1.6248</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1408</v>
+        <v>1.9413</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.4744</v>
+        <v>-2.8573</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.2586</v>
+        <v>-2.7017</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2157</v>
+        <v>-0.1556</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.58</v>
+        <v>-1.0248</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6195000000000001</v>
+        <v>-1.2608</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0395</v>
+        <v>0.2361</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8943</v>
+        <v>-1.8325</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6392</v>
+        <v>-1.4409</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2552</v>
+        <v>-0.3916</v>
       </c>
       <c r="P6" t="n">
-        <v>1.2321</v>
+        <v>1.6427</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.0801</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2321</v>
+        <v>4.7229</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5524</v>
+        <v>1.0595</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4416</v>
+        <v>1.3015</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1108</v>
+        <v>-0.2419</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3491</v>
+        <v>0.4715</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2402</v>
+        <v>1.1786</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5893</v>
+        <v>-0.7072000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2564</v>
+        <v>-0.006</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2018</v>
+        <v>-0.0701</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0546</v>
+        <v>0.064</v>
       </c>
       <c r="G7" t="n">
         <v>0.8558</v>
@@ -1000,13 +1000,13 @@
         <v>2.2588</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5138</v>
+        <v>-0.2635</v>
       </c>
       <c r="T7" t="n">
-        <v>0.244</v>
+        <v>0.3757</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7578</v>
+        <v>-0.6392</v>
       </c>
       <c r="V7" t="n">
         <v>-0.5983000000000001</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. MOURE COLOMBO</t>
+          <t>O. OKENCHI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8204</v>
+        <v>-0.4713</v>
       </c>
       <c r="E8" t="n">
-        <v>1.3221</v>
+        <v>-0.212</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.1425</v>
+        <v>-0.2593</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8981</v>
+        <v>-1.4744</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.756</v>
+        <v>-1.2586</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1422</v>
+        <v>-0.2157</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0514</v>
+        <v>-0.58</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0779</v>
+        <v>-0.6195000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0264</v>
+        <v>0.0395</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9495</v>
+        <v>-0.8943</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8338</v>
+        <v>-0.6392</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1157</v>
+        <v>-0.2552</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2053</v>
+        <v>1.2321</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2053</v>
+        <v>1.2321</v>
       </c>
       <c r="S8" t="n">
-        <v>1.051</v>
+        <v>0.1201</v>
       </c>
       <c r="T8" t="n">
-        <v>1.2707</v>
+        <v>0.1278</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2197</v>
+        <v>-0.0077</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.1786</v>
+        <v>-0.3491</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1786</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. MENDES KOVACS</t>
+          <t>E. MOURE COLOMBO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0008</v>
+        <v>-1.3591</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1504</v>
+        <v>0.6945</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8504</v>
+        <v>-2.0536</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.001</v>
+        <v>-0.8981</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.8715</v>
+        <v>-0.756</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8706</v>
+        <v>-0.1422</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1984</v>
+        <v>0.0514</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7877999999999999</v>
+        <v>0.0779</v>
       </c>
       <c r="L9" t="n">
-        <v>0.9863</v>
+        <v>-0.0264</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1994</v>
+        <v>-0.9495</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0837</v>
+        <v>-0.8338</v>
       </c>
       <c r="O9" t="n">
         <v>-0.1157</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2053</v>
+        <v>0.2053</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8481</v>
+        <v>0.2053</v>
       </c>
       <c r="S9" t="n">
-        <v>1.6244</v>
+        <v>0.5123</v>
       </c>
       <c r="T9" t="n">
-        <v>1.7045</v>
+        <v>0.6431</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.08019999999999999</v>
+        <v>-0.1307</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.4189</v>
+        <v>-1.1786</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.4189</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. KNOWLES</t>
+          <t>K. MENDES KOVACS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4436</v>
+        <v>-1.6441</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.3256</v>
+        <v>-0.8827</v>
       </c>
       <c r="F10" t="n">
-        <v>1.882</v>
+        <v>-0.7614</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.8573</v>
+        <v>-1.001</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.7017</v>
+        <v>-1.8715</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1556</v>
+        <v>0.8706</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.0248</v>
+        <v>0.1984</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.2608</v>
+        <v>-0.7877999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2361</v>
+        <v>0.9863</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.8325</v>
+        <v>-1.1994</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.4409</v>
+        <v>-1.0837</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3916</v>
+        <v>-0.1157</v>
       </c>
       <c r="P10" t="n">
-        <v>1.6427</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.0801</v>
+        <v>-2.0534</v>
       </c>
       <c r="R10" t="n">
-        <v>4.7229</v>
+        <v>1.8481</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7005</v>
+        <v>0.9811</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3993</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3012</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>0.4715</v>
+        <v>-1.4189</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.7072000000000001</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. RENANE</t>
+          <t>D. CUELLAR GARCIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4327</v>
+        <v>-1.8827</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4409</v>
+        <v>-2.3085</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9918</v>
+        <v>0.4258</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6504</v>
+        <v>-4.1413</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.0608</v>
+        <v>0.4084</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4104</v>
+        <v>-4.5497</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1597</v>
+        <v>-2.9901</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3664</v>
+        <v>1.6546</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5261</v>
+        <v>-4.6447</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8101</v>
+        <v>-1.1512</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6943</v>
+        <v>-1.2462</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1157</v>
+        <v>0.095</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4107</v>
+        <v>2.4641</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.2053</v>
       </c>
       <c r="R11" t="n">
-        <v>0.616</v>
+        <v>2.6694</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7741</v>
+        <v>0.275</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3952</v>
+        <v>0.8869</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3789</v>
+        <v>-0.612</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.4189</v>
+        <v>-0.4805</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.4189</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. CUELLAR GARCIA</t>
+          <t>P. RENANE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.4928</v>
+        <v>-1.9937</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.8</v>
+        <v>-0.0612</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3072</v>
+        <v>-1.9325</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.1413</v>
+        <v>-0.6504</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4084</v>
+        <v>-1.0608</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.5497</v>
+        <v>0.4104</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.9901</v>
+        <v>0.1597</v>
       </c>
       <c r="K12" t="n">
-        <v>1.6546</v>
+        <v>-0.3664</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.6447</v>
+        <v>0.5261</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.1512</v>
+        <v>-0.8101</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.2462</v>
+        <v>-0.6943</v>
       </c>
       <c r="O12" t="n">
-        <v>0.095</v>
+        <v>-0.1157</v>
       </c>
       <c r="P12" t="n">
-        <v>2.4641</v>
+        <v>0.4107</v>
       </c>
       <c r="Q12" t="n">
         <v>-0.2053</v>
       </c>
       <c r="R12" t="n">
-        <v>2.6694</v>
+        <v>0.616</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3352</v>
+        <v>-0.3352</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6046</v>
+        <v>-0.0156</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7305</v>
+        <v>-0.3196</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.4805</v>
+        <v>-1.4189</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.4805</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.620500000000003</v>
+        <v>10.6087</v>
       </c>
       <c r="E13" t="n">
-        <v>7.174</v>
+        <v>8.161799999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4465</v>
+        <v>2.4467</v>
       </c>
       <c r="G13" t="n">
         <v>-11.3952</v>
@@ -1444,7 +1444,7 @@
         <v>2.3694</v>
       </c>
       <c r="K13" t="n">
-        <v>4.952100000000001</v>
+        <v>4.952100000000002</v>
       </c>
       <c r="L13" t="n">
         <v>-2.5823</v>
@@ -1468,13 +1468,13 @@
         <v>27.7212</v>
       </c>
       <c r="S13" t="n">
-        <v>5.4427</v>
+        <v>6.430599999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>8.657100000000002</v>
+        <v>9.645000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.2144</v>
+        <v>-3.2143</v>
       </c>
       <c r="V13" t="n">
         <v>2.2259</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.3185</v>
+        <v>6.0184</v>
       </c>
       <c r="E14" t="n">
-        <v>3.5629</v>
+        <v>4.3997</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556</v>
+        <v>1.6187</v>
       </c>
       <c r="G14" t="n">
         <v>6.5026</v>
@@ -1546,13 +1546,13 @@
         <v>2.2588</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.5434</v>
+        <v>-0.8435</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6278</v>
+        <v>0.209</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.9156</v>
+        <v>-1.0525</v>
       </c>
       <c r="V14" t="n">
         <v>3.6447</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2035</v>
+        <v>1.3987</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3734</v>
+        <v>1.001</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8300999999999999</v>
+        <v>0.3977</v>
       </c>
       <c r="G15" t="n">
         <v>3.3477</v>
@@ -1624,13 +1624,13 @@
         <v>2.4641</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0086</v>
+        <v>-0.8134</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9068000000000001</v>
+        <v>-0.2791</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1018</v>
+        <v>-0.5343</v>
       </c>
       <c r="V15" t="n">
         <v>-0.1088</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Y. KOLO</t>
+          <t>G. COLOM BARRUFET</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2315</v>
+        <v>0.7773</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2151</v>
+        <v>0.5319</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0164</v>
+        <v>0.2454</v>
       </c>
       <c r="G16" t="n">
-        <v>3.5379</v>
+        <v>1.5416</v>
       </c>
       <c r="H16" t="n">
-        <v>2.4719</v>
+        <v>0.3209</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0659</v>
+        <v>1.2208</v>
       </c>
       <c r="J16" t="n">
-        <v>3.5449</v>
+        <v>1.4145</v>
       </c>
       <c r="K16" t="n">
-        <v>3.387</v>
+        <v>0.4282</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1579</v>
+        <v>0.9863</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.007</v>
+        <v>0.1271</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9151</v>
+        <v>-0.1074</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9081</v>
+        <v>0.2345</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.8481</v>
+        <v>-1.4374</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.0801</v>
+        <v>-2.0534</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2321</v>
+        <v>0.616</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1167</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1467</v>
+        <v>-0.0078</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.03</v>
+        <v>-0.4977</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.575</v>
+        <v>1.1786</v>
       </c>
       <c r="W16" t="n">
-        <v>-1.3963</v>
+        <v>1.1786</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1406</v>
+        <v>-0.1958</v>
       </c>
       <c r="E17" t="n">
-        <v>3.411</v>
+        <v>2.4696</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.2704</v>
+        <v>-2.6654</v>
       </c>
       <c r="G17" t="n">
         <v>-0.4048</v>
@@ -1780,13 +1780,13 @@
         <v>0.616</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2168</v>
+        <v>0.8804</v>
       </c>
       <c r="T17" t="n">
-        <v>2.1152</v>
+        <v>1.1738</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8984</v>
+        <v>-0.2934</v>
       </c>
       <c r="V17" t="n">
         <v>-1.2875</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. COLOM BARRUFET</t>
+          <t>Y. KOLO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1253</v>
+        <v>-0.3543</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2181</v>
+        <v>-0.4125</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.09279999999999999</v>
+        <v>0.0582</v>
       </c>
       <c r="G18" t="n">
-        <v>1.5416</v>
+        <v>3.5379</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3209</v>
+        <v>2.4719</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2208</v>
+        <v>1.0659</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4145</v>
+        <v>3.5449</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4282</v>
+        <v>3.387</v>
       </c>
       <c r="L18" t="n">
-        <v>0.9863</v>
+        <v>0.1579</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1271</v>
+        <v>-0.007</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1074</v>
+        <v>-0.9151</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2345</v>
+        <v>0.9081</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.4374</v>
+        <v>-1.8481</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.0534</v>
+        <v>-3.0801</v>
       </c>
       <c r="R18" t="n">
-        <v>0.616</v>
+        <v>1.2321</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1576</v>
+        <v>0.5308</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3216</v>
+        <v>0.5191</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8359</v>
+        <v>0.0118</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1786</v>
+        <v>-2.575</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1786</v>
+        <v>-1.3963</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5088</v>
+        <v>-0.4565</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6228</v>
+        <v>0.832</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1316</v>
+        <v>-1.2886</v>
       </c>
       <c r="G19" t="n">
         <v>1.0846</v>
@@ -1936,13 +1936,13 @@
         <v>1.2321</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.612</v>
+        <v>-0.5597</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2635</v>
+        <v>-0.0543</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3485</v>
+        <v>-0.5054</v>
       </c>
       <c r="V19" t="n">
         <v>-2.0082</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.2304</v>
+        <v>-2.7354</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.4691</v>
+        <v>-2.1552</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7614</v>
+        <v>-0.5800999999999999</v>
       </c>
       <c r="G20" t="n">
         <v>1.5775</v>
@@ -2014,13 +2014,13 @@
         <v>2.6694</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.541</v>
+        <v>-1.0459</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0699</v>
+        <v>0.2439</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.4711</v>
+        <v>-1.2898</v>
       </c>
       <c r="V20" t="n">
         <v>-1.4189</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0868</v>
+        <v>-2.8193</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.487</v>
+        <v>-1.964</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5998</v>
+        <v>-0.8552999999999999</v>
       </c>
       <c r="G21" t="n">
         <v>-0.0234</v>
@@ -2092,13 +2092,13 @@
         <v>1.8481</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1619</v>
+        <v>0.1056</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1354</v>
+        <v>0.6584</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.2973</v>
+        <v>-0.5528</v>
       </c>
       <c r="V21" t="n">
         <v>0.5893</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.814</v>
+        <v>-8.4642</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.8939</v>
+        <v>-7.1491</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9201</v>
+        <v>-1.3151</v>
       </c>
       <c r="G22" t="n">
         <v>-5.7686</v>
@@ -2170,13 +2170,13 @@
         <v>1.4374</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2483</v>
+        <v>-0.4019</v>
       </c>
       <c r="T22" t="n">
-        <v>2.0067</v>
+        <v>0.7514</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.7584</v>
+        <v>-1.1534</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2402</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-9.6206</v>
+        <v>-6.831100000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.4467</v>
+        <v>-2.446599999999998</v>
       </c>
       <c r="F23" t="n">
-        <v>-7.173999999999999</v>
+        <v>-4.3845</v>
       </c>
       <c r="G23" t="n">
         <v>11.3951</v>
@@ -2218,7 +2218,7 @@
         <v>6.2761</v>
       </c>
       <c r="I23" t="n">
-        <v>5.118900000000001</v>
+        <v>5.1189</v>
       </c>
       <c r="J23" t="n">
         <v>13.7648</v>
@@ -2248,13 +2248,13 @@
         <v>14.374</v>
       </c>
       <c r="S23" t="n">
-        <v>-5.4427</v>
+        <v>-2.6531</v>
       </c>
       <c r="T23" t="n">
         <v>3.2144</v>
       </c>
       <c r="U23" t="n">
-        <v>-8.657</v>
+        <v>-5.8675</v>
       </c>
       <c r="V23" t="n">
         <v>-2.226</v>
